--- a/docs/research_review/emotionclip_reid_papers.xlsx
+++ b/docs/research_review/emotionclip_reid_papers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Source\EmotionCLIP-ReID\outputs\019f6089-e841-7052-847b-c9e0c4537c48\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Source\EmotionCLIP-ReID\docs\research_review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4281C9-76AF-4621-93B7-0A3083966439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A800AE-96CC-4FCC-91AB-1EF81764D670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="24480" windowHeight="12915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="32 Papers" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
     <sheet name="Research Log" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'32 Papers'!$A$1:$Q$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'32 Papers'!$A$1:$Q$88</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="1132">
   <si>
     <t>Điểm cần phản biện</t>
   </si>
@@ -2670,18 +2670,6 @@
     <t>Dùng AU như prior có điều kiện/pseudo-AU có kiểm soát; bắt buộc có ablation.</t>
   </si>
   <si>
-    <t>Uncertainty-aware FER</t>
-  </si>
-  <si>
-    <t>FER có label ambiguity và overconfidence.</t>
-  </si>
-  <si>
-    <t>Uncertainty có thể làm mục tiêu nghiên cứu bị loãng nếu đưa vào trước khi descriptor baseline vững.</t>
-  </si>
-  <si>
-    <t>Đặt uncertainty là nhánh hiệu chỉnh/calibration sau semantic alignment.</t>
-  </si>
-  <si>
     <t>Multimodal MER</t>
   </si>
   <si>
@@ -2802,9 +2790,6 @@
     <t>Papers added</t>
   </si>
   <si>
-    <t>23 new papers, No. 54-76</t>
-  </si>
-  <si>
     <t>Quality-source rule</t>
   </si>
   <si>
@@ -2820,9 +2805,6 @@
     <t>Main clusters added</t>
   </si>
   <si>
-    <t>CLIP/VLM foundations; EmotionCLIP and CLIP-based FER/DFER; robust/noisy-label FER; dynamic FER; dataset/protocol foundations.</t>
-  </si>
-  <si>
     <t>Compatibility note</t>
   </si>
   <si>
@@ -3081,9 +3063,6 @@
     <t>CLIPER, DFER-CLIP, FineCLIPER, EA-CLIP, CEPrompt</t>
   </si>
   <si>
-    <t>MTAC, MAN, LDL, ULC-AG, UA-FER, 3WAUS, EDL Mirage, Rethinking Ambiguity</t>
-  </si>
-  <si>
     <t>Cross-dataset adaptation</t>
   </si>
   <si>
@@ -3124,6 +3103,327 @@
   </si>
   <si>
     <t>Exact title check; MPA-FER retained at No. 58.</t>
+  </si>
+  <si>
+    <t>Face-LLaVA: Facial Expression and Attribute Understanding through Instruction Tuning</t>
+  </si>
+  <si>
+    <t>Ashutosh Chaubey; Xulang Guan; Mohammad Soleymani</t>
+  </si>
+  <si>
+    <t>WACV 2026</t>
+  </si>
+  <si>
+    <t>Face MLLM / anatomy-guided cross-attention</t>
+  </si>
+  <si>
+    <t>Phát triển MLLM chuyên cho khuôn mặt, nhận diện biểu cảm/thuộc tính và sinh giải thích bằng ngôn ngữ.</t>
+  </si>
+  <si>
+    <t>Face-Region Guided Cross-Attention tích hợp hình học khuôn mặt với đặc trưng cục bộ; đánh giá trên 9 dataset và 5 tác vụ.</t>
+  </si>
+  <si>
+    <t>Mô hình instruction-tuned lớn, chi phí dữ liệu/compute cao; region guidance chưa tách lỗi landmark hoặc reliability của từng vùng.</t>
+  </si>
+  <si>
+    <t>FaceInstruct-1M; 9 datasets cho FER, AU, facial attributes, age và deepfake.</t>
+  </si>
+  <si>
+    <t>Vượt các MLLM mã nguồn mở và cạnh tranh với hệ thương mại trên nhiều tác vụ khuôn mặt; có đánh giá reasoning.</t>
+  </si>
+  <si>
+    <t>Face-specific visual encoder + Face-Region Guided Cross-Attention + multimodal instruction tuning.</t>
+  </si>
+  <si>
+    <t>https://openaccess.thecvf.com/content/WACV2026/html/Chaubey_Face-LLaVA_Facial_Expression_and_Attribute_Understanding_through_Instruction_Tuning_WACV_2026_paper.html</t>
+  </si>
+  <si>
+    <t>CVF Open Access / WACV 2026</t>
+  </si>
+  <si>
+    <t>Prior art gần nhất với landmark-region tokens và cross-attention; đặt ranh giới novelty cho soft anatomical routing có reliability và visual fallback.</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>Face-mask-aware Facial Expression Recognition based on Face Parsing and Vision Transformer</t>
+  </si>
+  <si>
+    <t>Bo Yang; Jianming Wu; Kazushi Ikeda; Gen Hattori; Masaru Sugano; Yusuke Iwasawa; Yutaka Matsuo</t>
+  </si>
+  <si>
+    <t>Pattern Recognition Letters 164, 173-182</t>
+  </si>
+  <si>
+    <t>Face parsing / occlusion-aware FER</t>
+  </si>
+  <si>
+    <t>Nhận diện biểu cảm khi đeo khẩu trang bằng cách phân tách vùng bị che và vùng còn quan sát được.</t>
+  </si>
+  <si>
+    <t>Kết hợp face parsing với cross-attention để tự thích nghi trọng số vùng masked/unmasked; trực tiếp kiểm chứng lợi ích của cấu trúc vùng.</t>
+  </si>
+  <si>
+    <t>Chuyên biệt cho khẩu trang và cần parsing mask; chưa mô hình hóa landmark uncertainty, blur hay domain shift tổng quát.</t>
+  </si>
+  <si>
+    <t>M-LFW-FER, M-KDDI-FER, M-FER-2013, M-CK+.</t>
+  </si>
+  <si>
+    <t>Báo cáo tốt hơn các phương pháp face-mask-aware và occlusion-aware FER trên bộ 3 lớp và 7 lớp.</t>
+  </si>
+  <si>
+    <t>Face-mask-aware face parsing + CNN/ViT feature encoding + cross-attention giữa vùng che và không che.</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0167865522003312</t>
+  </si>
+  <si>
+    <t>Elsevier / DOI 10.1016/j.patrec.2022.11.004</t>
+  </si>
+  <si>
+    <t>Prior art trực tiếp cho face-parsing region routing; cho thấy novelty không thể chỉ là chia vùng mà phải nằm ở missing/reliability-aware hybrid routing.</t>
+  </si>
+  <si>
+    <t>Evidential Deep Learning to Quantify Classification Uncertainty</t>
+  </si>
+  <si>
+    <t>Murat Sensoy; Lance Kaplan; Melih Kandemir</t>
+  </si>
+  <si>
+    <t>NeurIPS 2018</t>
+  </si>
+  <si>
+    <t>Evidential deep learning / Dirichlet uncertainty</t>
+  </si>
+  <si>
+    <t>Mô hình hóa classification uncertainty bằng Dirichlet evidence và subjective logic trong một mạng xác định.</t>
+  </si>
+  <si>
+    <t>Một forward pass tạo evidence, class probabilities và uncertainty; có thí nghiệm OOD và adversarial perturbation.</t>
+  </si>
+  <si>
+    <t>Ý nghĩa epistemic phụ thuộc giả định/parameterization evidence; các nghiên cứu sau chỉ ra EDL có thể hành xử gần energy-based OOD hơn.</t>
+  </si>
+  <si>
+    <t>MNIST-based classification, OOD và adversarial settings.</t>
+  </si>
+  <si>
+    <t>Bài gốc báo cáo OOD detection và độ bền adversarial tốt hơn các baseline được so sánh.</t>
+  </si>
+  <si>
+    <t>Non-negative evidence e; alpha=e+1; Dirichlet Bayes-risk objective với KL regularization.</t>
+  </si>
+  <si>
+    <t>https://proceedings.neurips.cc/paper/2018/hash/a981f2b708044d6fb4a71a1463242520-Abstract.html</t>
+  </si>
+  <si>
+    <t>NeurIPS proceedings</t>
+  </si>
+  <si>
+    <t>Nền tảng lý thuyết của EDL hiện tại và baseline softplus-evidence; cần đặt cạnh EDL Mirage và decoupled strength head.</t>
+  </si>
+  <si>
+    <t>On Calibration of Modern Neural Networks</t>
+  </si>
+  <si>
+    <t>Chuan Guo; Geoff Pleiss; Yu Sun; Kilian Q. Weinberger</t>
+  </si>
+  <si>
+    <t>ICML 2017 / PMLR 70</t>
+  </si>
+  <si>
+    <t>Calibration / temperature scaling</t>
+  </si>
+  <si>
+    <t>Đo mức calibration của neural network hiện đại và đánh giá các phương pháp hiệu chỉnh hậu xử lý.</t>
+  </si>
+  <si>
+    <t>Temperature scaling chỉ có một tham số, dễ triển khai nhưng thường hiệu chỉnh confidence rất hiệu quả trên validation.</t>
+  </si>
+  <si>
+    <t>Chỉ hiệu chỉnh confidence trên phân phối đã thấy; không cung cấp epistemic uncertainty và có thể suy giảm dưới domain shift.</t>
+  </si>
+  <si>
+    <t>CIFAR-100, ImageNet, 20 Newsgroups và các classification benchmarks.</t>
+  </si>
+  <si>
+    <t>Chứng minh nhiều mạng hiện đại bị miscalibrated và temperature scaling là baseline hậu xử lý mạnh.</t>
+  </si>
+  <si>
+    <t>Reliability diagrams, ECE và post-hoc temperature scaling trên validation logits.</t>
+  </si>
+  <si>
+    <t>https://proceedings.mlr.press/v70/guo17a.html</t>
+  </si>
+  <si>
+    <t>PMLR / ICML proceedings</t>
+  </si>
+  <si>
+    <t>Baseline calibration bắt buộc để kiểm tra reliability head có hơn một phép rescale logits đơn giản hay không.</t>
+  </si>
+  <si>
+    <t>Energy-based Out-of-distribution Detection</t>
+  </si>
+  <si>
+    <t>Weitang Liu; Xiaoyun Wang; John D. Owens; Yixuan Li</t>
+  </si>
+  <si>
+    <t>NeurIPS 2020</t>
+  </si>
+  <si>
+    <t>Energy score / OOD detection</t>
+  </si>
+  <si>
+    <t>Thay softmax confidence bằng energy score để phân biệt in-distribution và OOD.</t>
+  </si>
+  <si>
+    <t>Dùng được trực tiếp trên classifier đã huấn luyện và có thể bổ sung energy-margin training; đơn giản và hiệu quả.</t>
+  </si>
+  <si>
+    <t>Energy vẫn phụ thuộc logit scale/temperature, không tách class ambiguity khỏi input unreliability và không phải calibrated probability.</t>
+  </si>
+  <si>
+    <t>CIFAR-10, CIFAR-100, ImageNet và các OOD benchmarks phổ biến.</t>
+  </si>
+  <si>
+    <t>Trên CIFAR-10, energy score giảm FPR95 trung bình 18.03 điểm phần trăm so với softmax score trong thiết lập được báo cáo.</t>
+  </si>
+  <si>
+    <t>E(x)=-T logsumexp(z/T), dùng làm OOD score hoặc mục tiêu margin-based training.</t>
+  </si>
+  <si>
+    <t>https://proceedings.neurips.cc/paper_files/paper/2020/hash/f5496252609c43eb8a3d147ab9b9c006-Abstract.html</t>
+  </si>
+  <si>
+    <t>Baseline OOD được yêu cầu trong gap analysis và là đối chứng trực tiếp với cách diễn giải EDL như energy-based detector.</t>
+  </si>
+  <si>
+    <t>Dropout as a Bayesian Approximation: Representing Model Uncertainty in Deep Learning</t>
+  </si>
+  <si>
+    <t>Yarin Gal; Zoubin Ghahramani</t>
+  </si>
+  <si>
+    <t>ICML 2016 / PMLR 48</t>
+  </si>
+  <si>
+    <t>MC dropout / approximate Bayesian uncertainty</t>
+  </si>
+  <si>
+    <t>Diễn giải dropout như approximate Bayesian inference để lấy predictive/model uncertainty.</t>
+  </si>
+  <si>
+    <t>Có thể bổ sung vào mạng đã dùng dropout và ước lượng uncertainty bằng nhiều stochastic forward passes.</t>
+  </si>
+  <si>
+    <t>Tăng chi phí inference theo số lần lấy mẫu; nhạy với dropout rate và chất lượng xấp xỉ posterior.</t>
+  </si>
+  <si>
+    <t>MNIST cùng các regression/classification benchmarks; minh họa thêm trong deep reinforcement learning.</t>
+  </si>
+  <si>
+    <t>Cải thiện predictive log-likelihood và RMSE so với các phương pháp được so sánh trong bài.</t>
+  </si>
+  <si>
+    <t>Giữ dropout hoạt động khi inference; tổng hợp trung bình và phương sai qua T stochastic passes.</t>
+  </si>
+  <si>
+    <t>https://proceedings.mlr.press/v48/gal16.html</t>
+  </si>
+  <si>
+    <t>Baseline sampling-based uncertainty nhẹ hơn ensemble, cần so với single-pass decoupled reliability head.</t>
+  </si>
+  <si>
+    <t>Simple and Scalable Predictive Uncertainty Estimation using Deep Ensembles</t>
+  </si>
+  <si>
+    <t>Balaji Lakshminarayanan; Alexander Pritzel; Charles Blundell</t>
+  </si>
+  <si>
+    <t>NIPS 2017</t>
+  </si>
+  <si>
+    <t>Deep ensembles / predictive uncertainty</t>
+  </si>
+  <si>
+    <t>Ước lượng predictive uncertainty bằng ensemble các mạng huấn luyện độc lập.</t>
+  </si>
+  <si>
+    <t>Baseline mạnh, dễ song song hóa, calibration tốt và phản ứng với dataset shift/OOD.</t>
+  </si>
+  <si>
+    <t>Chi phí train, lưu trữ và inference tăng theo số member; uncertainty trộn model diversity với optimization randomness.</t>
+  </si>
+  <si>
+    <t>Regression/classification benchmarks, dataset shift/OOD và ImageNet.</t>
+  </si>
+  <si>
+    <t>Báo cáo uncertainty được hiệu chỉnh ngang hoặc tốt hơn approximate Bayesian neural networks và mở rộng tới ImageNet.</t>
+  </si>
+  <si>
+    <t>Huấn luyện nhiều model với khởi tạo độc lập; trung bình predictive distributions và đo disagreement.</t>
+  </si>
+  <si>
+    <t>https://proceedings.neurips.cc/paper_files/paper/2017/hash/9ef2ed4b7fd2c810847ffa5fa85bce38-Abstract.html</t>
+  </si>
+  <si>
+    <t>NIPS proceedings</t>
+  </si>
+  <si>
+    <t>Baseline mạnh nhất để đánh giá lợi ích/chi phí của single-model reliability head và báo cáo compute trade-off.</t>
+  </si>
+  <si>
+    <t>Uncertainty-aware FER/UQ</t>
+  </si>
+  <si>
+    <t>UA-FER, 3WAUS, EDL, EDL Mirage, Temperature Scaling, Energy, MC Dropout, Deep Ensembles, Rethinking Ambiguity</t>
+  </si>
+  <si>
+    <t>Có cả mô hình Dirichlet và các baseline calibration/OOD/sampling để kiểm tra độ tin cậy.</t>
+  </si>
+  <si>
+    <t>EDL có thể không phản ánh epistemic uncertainty; temperature/energy không tách intrinsic ambiguity khỏi input unreliability; sampling/ensemble tốn compute.</t>
+  </si>
+  <si>
+    <t>So sánh softmax CE, temperature scaling, energy, MC dropout/deep ensemble, EDL cũ và decoupled reliability head.</t>
+  </si>
+  <si>
+    <t>Anatomy/region grounding</t>
+  </si>
+  <si>
+    <t>Face-LLaVA, Face-mask-aware FER, LA-Net, Region Attention Networks</t>
+  </si>
+  <si>
+    <t>Landmark, face parsing và region cross-attention hỗ trợ tín hiệu cục bộ và robustness với che khuất.</t>
+  </si>
+  <si>
+    <t>Hard region hoặc unconditional cross-attention có thể tin geometry sai; chưa tách disagreement thật khỏi lỗi landmark/blur/occlusion.</t>
+  </si>
+  <si>
+    <t>Dùng soft anatomical routing + region quality gate + learned free-attention fallback; đánh giá hit-rate, deletion và landmark perturbation.</t>
+  </si>
+  <si>
+    <t>2026-07-18 update</t>
+  </si>
+  <si>
+    <t>Added 7 unique papers as No. 81-87; the main sheet now contains 87 papers.</t>
+  </si>
+  <si>
+    <t>Face-LLaVA; Face-mask-aware FER; Evidential Deep Learning; On Calibration of Modern Neural Networks; Energy-based OOD Detection; MC Dropout; Deep Ensembles.</t>
+  </si>
+  <si>
+    <t>Anatomy/region grounding; face parsing under occlusion; Dirichlet EDL foundation; calibration, OOD and sampling/ensemble uncertainty baselines.</t>
+  </si>
+  <si>
+    <t>Used CVF Open Access, Elsevier/DOI, NeurIPS proceedings and PMLR/ICML official pages; no blog-only or mirror-only source.</t>
+  </si>
+  <si>
+    <t>Exact-title and normalized-title check against No. 1-80; no duplicate row added.</t>
+  </si>
+  <si>
+    <t>7 new papers, No. 81-87</t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3944,7 +4244,7 @@
         <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>90</v>
@@ -3968,16 +4268,16 @@
         <v>96</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="P6" s="18" t="s">
         <v>51</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -4156,7 +4456,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>130</v>
@@ -4180,16 +4480,16 @@
         <v>136</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="P10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="Q10" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -4253,7 +4553,7 @@
         <v>148</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="D12" s="5">
         <v>2024</v>
@@ -4262,7 +4562,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>149</v>
@@ -4286,16 +4586,16 @@
         <v>154</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="P12" s="18" t="s">
         <v>51</v>
       </c>
       <c r="Q12" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -5240,16 +5540,16 @@
         <v>348</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="P30" s="18" t="s">
         <v>51</v>
       </c>
       <c r="Q30" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -5293,16 +5593,16 @@
         <v>357</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="P31" s="18" t="s">
         <v>51</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -6850,7 +7150,7 @@
         <v>676</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="D61" s="18">
         <v>2026</v>
@@ -6859,7 +7159,7 @@
         <v>55</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="G61" s="18" t="s">
         <v>677</v>
@@ -6883,16 +7183,16 @@
         <v>683</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="P61" s="18" t="s">
         <v>685</v>
       </c>
       <c r="Q61" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -6903,7 +7203,7 @@
         <v>686</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D62" s="18">
         <v>2024</v>
@@ -6912,7 +7212,7 @@
         <v>40</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="G62" s="18" t="s">
         <v>687</v>
@@ -6936,16 +7236,16 @@
         <v>692</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="P62" s="18" t="s">
         <v>693</v>
       </c>
       <c r="Q62" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -7486,7 +7786,7 @@
         <v>808</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="D73" s="18">
         <v>2023</v>
@@ -7495,7 +7795,7 @@
         <v>40</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="G73" s="18" t="s">
         <v>809</v>
@@ -7519,16 +7819,16 @@
         <v>814</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="P73" s="18" t="s">
         <v>815</v>
       </c>
       <c r="Q73" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -7645,7 +7945,7 @@
         <v>837</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="D76" s="18">
         <v>2023</v>
@@ -7654,7 +7954,7 @@
         <v>40</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="G76" s="18" t="s">
         <v>838</v>
@@ -7678,16 +7978,16 @@
         <v>843</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="P76" s="18" t="s">
         <v>844</v>
       </c>
       <c r="Q76" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -7748,10 +8048,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="D78" s="18">
         <v>2024</v>
@@ -7760,40 +8060,40 @@
         <v>55</v>
       </c>
       <c r="F78" s="18" t="s">
+        <v>960</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>961</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>962</v>
+      </c>
+      <c r="I78" s="18" t="s">
+        <v>963</v>
+      </c>
+      <c r="J78" s="18" t="s">
+        <v>964</v>
+      </c>
+      <c r="K78" s="18" t="s">
+        <v>965</v>
+      </c>
+      <c r="L78" s="18" t="s">
         <v>966</v>
       </c>
-      <c r="G78" s="18" t="s">
+      <c r="M78" s="18" t="s">
         <v>967</v>
       </c>
-      <c r="H78" s="18" t="s">
+      <c r="N78" s="18" t="s">
         <v>968</v>
       </c>
-      <c r="I78" s="18" t="s">
+      <c r="O78" s="18" t="s">
         <v>969</v>
       </c>
-      <c r="J78" s="18" t="s">
+      <c r="P78" s="18" t="s">
         <v>970</v>
       </c>
-      <c r="K78" s="18" t="s">
-        <v>971</v>
-      </c>
-      <c r="L78" s="18" t="s">
-        <v>972</v>
-      </c>
-      <c r="M78" s="18" t="s">
-        <v>973</v>
-      </c>
-      <c r="N78" s="18" t="s">
-        <v>974</v>
-      </c>
-      <c r="O78" s="18" t="s">
-        <v>975</v>
-      </c>
-      <c r="P78" s="18" t="s">
-        <v>976</v>
-      </c>
       <c r="Q78" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -7801,10 +8101,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="D79" s="18">
         <v>2024</v>
@@ -7813,40 +8113,40 @@
         <v>40</v>
       </c>
       <c r="F79" s="18" t="s">
+        <v>973</v>
+      </c>
+      <c r="G79" s="18" t="s">
+        <v>974</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>975</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>976</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>977</v>
+      </c>
+      <c r="K79" s="18" t="s">
+        <v>978</v>
+      </c>
+      <c r="L79" s="18" t="s">
         <v>979</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="M79" s="18" t="s">
         <v>980</v>
       </c>
-      <c r="H79" s="18" t="s">
+      <c r="N79" s="18" t="s">
         <v>981</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="O79" s="18" t="s">
         <v>982</v>
       </c>
-      <c r="J79" s="18" t="s">
+      <c r="P79" s="18" t="s">
         <v>983</v>
       </c>
-      <c r="K79" s="18" t="s">
-        <v>984</v>
-      </c>
-      <c r="L79" s="18" t="s">
-        <v>985</v>
-      </c>
-      <c r="M79" s="18" t="s">
-        <v>986</v>
-      </c>
-      <c r="N79" s="18" t="s">
-        <v>987</v>
-      </c>
-      <c r="O79" s="18" t="s">
-        <v>988</v>
-      </c>
-      <c r="P79" s="18" t="s">
-        <v>989</v>
-      </c>
       <c r="Q79" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -7854,10 +8154,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="D80" s="18">
         <v>2026</v>
@@ -7866,40 +8166,40 @@
         <v>55</v>
       </c>
       <c r="F80" s="18" t="s">
+        <v>986</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>987</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>988</v>
+      </c>
+      <c r="I80" s="18" t="s">
+        <v>989</v>
+      </c>
+      <c r="J80" s="18" t="s">
+        <v>990</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="L80" s="18" t="s">
         <v>992</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="M80" s="18" t="s">
         <v>993</v>
       </c>
-      <c r="H80" s="18" t="s">
+      <c r="N80" s="18" t="s">
         <v>994</v>
       </c>
-      <c r="I80" s="18" t="s">
+      <c r="O80" s="18" t="s">
         <v>995</v>
       </c>
-      <c r="J80" s="18" t="s">
+      <c r="P80" s="18" t="s">
         <v>996</v>
       </c>
-      <c r="K80" s="18" t="s">
-        <v>997</v>
-      </c>
-      <c r="L80" s="18" t="s">
-        <v>998</v>
-      </c>
-      <c r="M80" s="18" t="s">
-        <v>999</v>
-      </c>
-      <c r="N80" s="18" t="s">
-        <v>1000</v>
-      </c>
-      <c r="O80" s="18" t="s">
-        <v>1001</v>
-      </c>
-      <c r="P80" s="18" t="s">
-        <v>1002</v>
-      </c>
       <c r="Q80" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -7907,10 +8207,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="D81" s="18">
         <v>2026</v>
@@ -7919,44 +8219,415 @@
         <v>40</v>
       </c>
       <c r="F81" s="18" t="s">
+        <v>999</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J81" s="18" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L81" s="18" t="s">
         <v>1005</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="M81" s="18" t="s">
         <v>1006</v>
       </c>
-      <c r="H81" s="18" t="s">
+      <c r="N81" s="18" t="s">
         <v>1007</v>
       </c>
-      <c r="I81" s="18" t="s">
+      <c r="O81" s="18" t="s">
         <v>1008</v>
       </c>
-      <c r="J81" s="18" t="s">
+      <c r="P81" s="18" t="s">
         <v>1009</v>
       </c>
-      <c r="K81" s="18" t="s">
-        <v>1010</v>
-      </c>
-      <c r="L81" s="18" t="s">
-        <v>1011</v>
-      </c>
-      <c r="M81" s="18" t="s">
-        <v>1012</v>
-      </c>
-      <c r="N81" s="18" t="s">
-        <v>1013</v>
-      </c>
-      <c r="O81" s="18" t="s">
-        <v>1014</v>
-      </c>
-      <c r="P81" s="18" t="s">
-        <v>1015</v>
-      </c>
       <c r="Q81" s="22" t="s">
-        <v>938</v>
+        <v>932</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="18">
+        <v>81</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D82" s="18">
+        <v>2026</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M82" s="18" t="s">
+        <v>1034</v>
+      </c>
+      <c r="N82" s="18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="O82" s="18" t="s">
+        <v>1036</v>
+      </c>
+      <c r="P82" s="18" t="s">
+        <v>1037</v>
+      </c>
+      <c r="Q82" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="18">
+        <v>82</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D83" s="18">
+        <v>2022</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M83" s="18" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N83" s="18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O83" s="18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P83" s="18" t="s">
+        <v>1051</v>
+      </c>
+      <c r="Q83" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>83</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D84" s="18">
+        <v>2018</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I84" s="18" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J84" s="18" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K84" s="18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M84" s="18" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N84" s="18" t="s">
+        <v>1062</v>
+      </c>
+      <c r="O84" s="18" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P84" s="18" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q84" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="18">
+        <v>84</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D85" s="18">
+        <v>2017</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I85" s="18" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J85" s="18" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M85" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N85" s="18" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O85" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P85" s="18" t="s">
+        <v>1077</v>
+      </c>
+      <c r="Q85" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="18">
+        <v>85</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D86" s="18">
+        <v>2020</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G86" s="18" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J86" s="18" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K86" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M86" s="18" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N86" s="18" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O86" s="18" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P86" s="18" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Q86" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="18">
+        <v>86</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D87" s="18">
+        <v>2016</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I87" s="18" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J87" s="18" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="M87" s="18" t="s">
+        <v>1099</v>
+      </c>
+      <c r="N87" s="18" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O87" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P87" s="18" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Q87" s="22" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="18">
+        <v>87</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D88" s="18">
+        <v>2017</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G88" s="18" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H88" s="18" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I88" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J88" s="18" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K88" s="18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L88" s="18" t="s">
+        <v>1110</v>
+      </c>
+      <c r="M88" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="N88" s="18" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O88" s="18" t="s">
+        <v>1113</v>
+      </c>
+      <c r="P88" s="18" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q88" s="22" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q77" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Q88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -8018,7 +8689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8083,7 +8754,7 @@
         <v>871</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>872</v>
@@ -8114,70 +8785,87 @@
     </row>
     <row r="6" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>880</v>
+        <v>1115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1017</v>
+        <v>1116</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>881</v>
+        <v>1117</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>882</v>
+        <v>1118</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>883</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>884</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>886</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>887</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
+        <v>885</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>886</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>887</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>888</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>889</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>890</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>891</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>892</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>1022</v>
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
@@ -8196,58 +8884,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -8358,58 +9046,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -8419,7 +9107,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -8428,58 +9116,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>938</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>924</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>930</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -8488,10 +9176,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -8680,34 +9368,74 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>1031</v>
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>920</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
